--- a/data/trans_dic/P1427-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1427-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,54</t>
+          <t>1,36; 3,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,48</t>
+          <t>0,71; 2,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,04</t>
+          <t>3,22; 5,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,59</t>
+          <t>1,95; 4,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,75</t>
+          <t>1,46; 3,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 7,93</t>
+          <t>5,11; 7,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,51</t>
+          <t>1,85; 3,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,82</t>
+          <t>1,22; 2,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 6,57</t>
+          <t>4,44; 6,19</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,28</t>
+          <t>1,27; 3,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,42</t>
+          <t>0,36; 1,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,6</t>
+          <t>2,27; 4,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,91</t>
+          <t>1,71; 3,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,67</t>
+          <t>0,95; 2,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,11</t>
+          <t>2,45; 4,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,25</t>
+          <t>1,75; 3,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,74</t>
+          <t>0,8; 1,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,51</t>
+          <t>2,54; 3,73</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,44</t>
+          <t>0,68; 2,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,09</t>
+          <t>0,39; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,48</t>
+          <t>1,4; 3,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,57</t>
+          <t>1,29; 3,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,4</t>
+          <t>1,11; 3,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,95</t>
+          <t>3,52; 5,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,67</t>
+          <t>1,16; 2,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,22</t>
+          <t>0,99; 2,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,87</t>
+          <t>2,76; 4,37</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,52</t>
+          <t>1,41; 3,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,07</t>
+          <t>0,64; 2,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,35</t>
+          <t>2,33; 4,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,97</t>
+          <t>1,83; 3,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,36</t>
+          <t>1,97; 4,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,23</t>
+          <t>3,41; 5,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,4</t>
+          <t>1,81; 3,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,83</t>
+          <t>1,54; 2,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,9</t>
+          <t>3,07; 4,42</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,51</t>
+          <t>1,54; 2,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,42</t>
+          <t>0,75; 1,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,64</t>
+          <t>2,61; 3,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,28</t>
+          <t>2,14; 3,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,81</t>
+          <t>1,78; 2,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,97</t>
+          <t>3,93; 4,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 2,7</t>
+          <t>1,95; 2,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,01</t>
+          <t>1,39; 2,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,14</t>
+          <t>3,46; 4,19</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29081</t>
+          <t>29237</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44598</t>
+          <t>46032</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73679</t>
+          <t>75269</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9052; 24886</t>
+          <t>9534; 25746</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4295; 16721</t>
+          <t>4810; 16698</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21763; 38399</t>
+          <t>22252; 38252</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13369; 31970</t>
+          <t>13592; 32184</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8946; 25208</t>
+          <t>9824; 26427</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37344; 53535</t>
+          <t>37416; 54356</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25435; 49197</t>
+          <t>25855; 49751</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17073; 38045</t>
+          <t>16488; 37688</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62496; 86132</t>
+          <t>63175; 88044</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30291</t>
+          <t>32096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>33527</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61033</t>
+          <t>65623</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11970; 33356</t>
+          <t>12922; 35646</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3569; 14484</t>
+          <t>3641; 15099</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14241; 42922</t>
+          <t>23797; 45173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18296; 40219</t>
+          <t>17547; 40452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9944; 27829</t>
+          <t>9957; 27964</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23302; 39327</t>
+          <t>26257; 42771</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36008; 66438</t>
+          <t>35834; 65553</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16327; 35931</t>
+          <t>16521; 36003</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38460; 75405</t>
+          <t>53747; 78977</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32809</t>
+          <t>38296</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49039</t>
+          <t>56148</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5091; 18467</t>
+          <t>5141; 19483</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3469; 15902</t>
+          <t>2928; 15043</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10067; 24346</t>
+          <t>11182; 27091</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9692; 27751</t>
+          <t>10029; 28192</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8894; 26698</t>
+          <t>8686; 26469</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14781; 46208</t>
+          <t>28549; 48383</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18710; 41050</t>
+          <t>17792; 40688</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14459; 34246</t>
+          <t>15367; 36116</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29182; 63255</t>
+          <t>44396; 70303</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29842</t>
+          <t>30434</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48642</t>
+          <t>47573</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>78485</t>
+          <t>78007</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12925; 33398</t>
+          <t>13376; 34154</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5501; 19409</t>
+          <t>6004; 19207</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21444; 40272</t>
+          <t>23074; 40576</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19728; 41807</t>
+          <t>19203; 41182</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21142; 45476</t>
+          <t>20515; 44112</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36899; 68000</t>
+          <t>38120; 59735</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36585; 67897</t>
+          <t>36112; 64950</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28791; 56119</t>
+          <t>30415; 57214</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62409; 98829</t>
+          <t>64806; 93168</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>109619</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>156792</t>
+          <t>165427</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>262236</t>
+          <t>275046</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>53484; 86156</t>
+          <t>52928; 88371</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25073; 48345</t>
+          <t>25492; 48016</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80934; 125683</t>
+          <t>92165; 128153</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75593; 116739</t>
+          <t>76098; 117673</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>63420; 99565</t>
+          <t>63030; 100160</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>124658; 181666</t>
+          <t>146671; 186357</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>136186; 188561</t>
+          <t>136074; 187911</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>93876; 139477</t>
+          <t>96676; 141206</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>226231; 294663</t>
+          <t>250908; 304092</t>
         </is>
       </c>
     </row>
